--- a/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_SFH_from_2015_investment_decision.xlsx
+++ b/data/Lüterkofen-Ichertswil/investment_decision/Lüterkofen_SFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>59.75312874392491</v>
+        <v>20.62750686141732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>13356.03394289321</v>
       </c>
       <c r="F2" t="n">
-        <v>59.75312874392492</v>
+        <v>20.62750686141732</v>
       </c>
       <c r="G2" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="H2" t="n">
-        <v>59.75312874392493</v>
+        <v>20.60985817486566</v>
       </c>
       <c r="I2" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="J2" t="n">
-        <v>59.75312874392495</v>
+        <v>20.62750686141732</v>
       </c>
       <c r="K2" t="n">
         <v>13356.03394289321</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>86.35067952077533</v>
+        <v>37.8955191296169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>13356.03394289321</v>
       </c>
       <c r="F3" t="n">
-        <v>81.4090222474407</v>
+        <v>37.8955191296169</v>
       </c>
       <c r="G3" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="H3" t="n">
-        <v>82.2133765036711</v>
+        <v>38.3034223582755</v>
       </c>
       <c r="I3" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="J3" t="n">
-        <v>82.22502008241801</v>
+        <v>38.3034223582755</v>
       </c>
       <c r="K3" t="n">
         <v>13356.03394289321</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>86.35067952077534</v>
+        <v>49.54799682839499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>13356.03394289321</v>
       </c>
       <c r="F4" t="n">
-        <v>81.4090222474407</v>
+        <v>49.33191244469484</v>
       </c>
       <c r="G4" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="H4" t="n">
-        <v>82.2133765036711</v>
+        <v>48.19347343348591</v>
       </c>
       <c r="I4" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="J4" t="n">
-        <v>82.22502008241801</v>
+        <v>49.36814049343945</v>
       </c>
       <c r="K4" t="n">
         <v>13356.03394289321</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>86.35067952077534</v>
+        <v>49.54799682839499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>13356.03394289321</v>
       </c>
       <c r="F5" t="n">
-        <v>81.4090222474407</v>
+        <v>49.33191244469484</v>
       </c>
       <c r="G5" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="H5" t="n">
-        <v>82.2133765036711</v>
+        <v>49.79377877975032</v>
       </c>
       <c r="I5" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="J5" t="n">
-        <v>82.22502008241801</v>
+        <v>49.36814049343945</v>
       </c>
       <c r="K5" t="n">
         <v>13356.03394289321</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>86.35067952077534</v>
+        <v>98.45522307019387</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>13356.03394289321</v>
       </c>
       <c r="F6" t="n">
-        <v>81.4090222474407</v>
+        <v>98.45522307019388</v>
       </c>
       <c r="G6" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="H6" t="n">
-        <v>82.2133765036711</v>
+        <v>93.52262238126829</v>
       </c>
       <c r="I6" t="n">
         <v>13356.03394289321</v>
       </c>
       <c r="J6" t="n">
-        <v>82.5018392901849</v>
+        <v>93.09690910379238</v>
       </c>
       <c r="K6" t="n">
         <v>13356.03394289321</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Lüterkofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Lüterkofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>20.03405091433982</v>
+        <v>32.80297887640449</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.006182396724705884</v>
+        <v>0.004963665553508199</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006182396724705884</v>
+        <v>0.004963665553508199</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.006182396724705884</v>
+        <v>0.004969829777352539</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.006182396724705884</v>
+        <v>0.004963665553508199</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.006182396724705884</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.006744432790588235</v>
+        <v>0.005901378691764707</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.7687667866671809</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>5.016171888</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.79148996</v>
       </c>
       <c r="G19" t="n">
         <v>5.016171888</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.4378269233350715</v>
       </c>
       <c r="I19" t="n">
         <v>5.016171888</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.4261861238213659</v>
       </c>
       <c r="K19" t="n">
         <v>5.016171888</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>1.781645676007327</v>
+        <v>1.665796805824685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>5.016171888</v>
       </c>
       <c r="F20" t="n">
-        <v>1.781645676007328</v>
+        <v>1.665796805824685</v>
       </c>
       <c r="G20" t="n">
         <v>5.016171888</v>
       </c>
       <c r="H20" t="n">
-        <v>1.781645676007328</v>
+        <v>0.8381530418536922</v>
       </c>
       <c r="I20" t="n">
         <v>5.016171888</v>
       </c>
       <c r="J20" t="n">
-        <v>1.781645676007328</v>
+        <v>0.8333707192935563</v>
       </c>
       <c r="K20" t="n">
         <v>5.016171888</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>1.781645676007327</v>
+        <v>1.665796805824685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>5.016171888</v>
       </c>
       <c r="F21" t="n">
-        <v>1.781645676007328</v>
+        <v>1.665796805824685</v>
       </c>
       <c r="G21" t="n">
         <v>5.016171888</v>
       </c>
       <c r="H21" t="n">
-        <v>1.781645676007328</v>
+        <v>0.8381530418536922</v>
       </c>
       <c r="I21" t="n">
         <v>5.016171888</v>
       </c>
       <c r="J21" t="n">
-        <v>1.781645676007328</v>
+        <v>0.8333707192935563</v>
       </c>
       <c r="K21" t="n">
         <v>5.016171888</v>
@@ -1513,13 +1513,13 @@
         <v>5.016171888</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.2997139730852918</v>
       </c>
       <c r="I29" t="n">
         <v>5.016171888</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2904634699881576</v>
       </c>
       <c r="K29" t="n">
         <v>5.016171888</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.14929083</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>5.016171888</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.14929083</v>
       </c>
       <c r="G30" t="n">
         <v>5.016171888</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.9769345939709928</v>
       </c>
       <c r="I30" t="n">
         <v>5.016171888</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.9817169165311285</v>
       </c>
       <c r="K30" t="n">
         <v>5.016171888</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.14929083</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>5.016171888</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.14929083</v>
       </c>
       <c r="G31" t="n">
         <v>5.016171888</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.9769345939709928</v>
       </c>
       <c r="I31" t="n">
         <v>5.016171888</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.9817169165311286</v>
       </c>
       <c r="K31" t="n">
         <v>5.016171888</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>5.196573681518384</v>
+        <v>5.141149846105815</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F54" t="n">
-        <v>5.122423979615781</v>
+        <v>5.064194813491354</v>
       </c>
       <c r="G54" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H54" t="n">
-        <v>5.133282888503307</v>
+        <v>5.143368357123114</v>
       </c>
       <c r="I54" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J54" t="n">
-        <v>5.189485902522379</v>
+        <v>5.0651864376913</v>
       </c>
       <c r="K54" t="n">
         <v>19.89477274555362</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>6.150241856056134</v>
+        <v>6.070109415892887</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F55" t="n">
-        <v>5.923611962327325</v>
+        <v>6.005074261043182</v>
       </c>
       <c r="G55" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H55" t="n">
-        <v>5.742221563195772</v>
+        <v>6.076836891959631</v>
       </c>
       <c r="I55" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J55" t="n">
-        <v>6.133330615989873</v>
+        <v>6.021710167727112</v>
       </c>
       <c r="K55" t="n">
         <v>19.89477274555362</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>6.150241856056134</v>
+        <v>6.259278441193938</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F56" t="n">
-        <v>5.923611962327325</v>
+        <v>6.078824858279124</v>
       </c>
       <c r="G56" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H56" t="n">
-        <v>5.742221563195772</v>
+        <v>6.116606068477218</v>
       </c>
       <c r="I56" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J56" t="n">
-        <v>6.133330615989873</v>
+        <v>6.037891789019222</v>
       </c>
       <c r="K56" t="n">
         <v>19.89477274555362</v>
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7152943844924112</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2728,19 +2728,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F62" t="n">
-        <v>0.715294384492411</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7152943844924116</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J62" t="n">
-        <v>0.7152943844924112</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>19.89477274555362</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>3.224911807793825</v>
+        <v>1.350388057549334</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F63" t="n">
-        <v>3.333918953529148</v>
+        <v>1.350388057549334</v>
       </c>
       <c r="G63" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H63" t="n">
-        <v>3.31617584493583</v>
+        <v>1.364384359950236</v>
       </c>
       <c r="I63" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J63" t="n">
-        <v>3.315919001287001</v>
+        <v>1.364384359950236</v>
       </c>
       <c r="K63" t="n">
         <v>19.89477274555362</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>4.028338126275441</v>
+        <v>2.099770411138138</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F64" t="n">
-        <v>4.211494973913367</v>
+        <v>2.178755422506944</v>
       </c>
       <c r="G64" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H64" t="n">
-        <v>4.182892956432523</v>
+        <v>2.128105107470962</v>
       </c>
       <c r="I64" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J64" t="n">
-        <v>4.126433098764623</v>
+        <v>2.195251758484475</v>
       </c>
       <c r="K64" t="n">
         <v>19.89477274555362</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>4.07466995173769</v>
+        <v>2.170810841351068</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F65" t="n">
-        <v>4.410306991201823</v>
+        <v>2.237875974955116</v>
       </c>
       <c r="G65" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H65" t="n">
-        <v>4.573954281740058</v>
+        <v>2.187574274513671</v>
       </c>
       <c r="I65" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J65" t="n">
-        <v>4.182588385297128</v>
+        <v>2.248194505036249</v>
       </c>
       <c r="K65" t="n">
         <v>19.89477274555362</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>4.782577432586879</v>
+        <v>1.522188761161205</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>19.89477274555362</v>
       </c>
       <c r="F66" t="n">
-        <v>5.118214472051012</v>
+        <v>1.702642344076021</v>
       </c>
       <c r="G66" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="H66" t="n">
-        <v>5.281861762589246</v>
+        <v>1.801036166407624</v>
       </c>
       <c r="I66" t="n">
         <v>19.89477274555362</v>
       </c>
       <c r="J66" t="n">
-        <v>4.884389560092634</v>
+        <v>1.889825309449114</v>
       </c>
       <c r="K66" t="n">
         <v>19.89477274555362</v>
